--- a/SA2502049_Automation_Project/MyFirstExcelFile.xlsx
+++ b/SA2502049_Automation_Project/MyFirstExcelFile.xlsx
@@ -12,11 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
-  <si>
-    <t>Piyush</t>
-  </si>
-</sst>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="0" uniqueCount="0"/>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -63,8 +59,8 @@
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="s" s="0">
-        <v>0</v>
+      <c r="A1" t="n" s="0">
+        <v>20.0</v>
       </c>
     </row>
   </sheetData>
